--- a/www/ig/fhir/core/StructureDefinition-fr-core-related-person.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-related-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="397">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson</t>
+    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -418,7 +418,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -431,14 +431,14 @@
     <t>RelatedPerson.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -460,6 +460,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0</t>
+  </si>
+  <si>
     <t>RelatedPerson.meta.security</t>
   </si>
   <si>
@@ -482,7 +485,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -506,7 +509,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -549,7 +552,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -688,7 +691,7 @@
     <t>RelatedPerson.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -723,7 +726,7 @@
     <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -748,7 +751,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.2.0</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:Role.id</t>
@@ -967,7 +970,7 @@
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type|2.2.0</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:RelationType.id</t>
@@ -1009,43 +1012,36 @@
     <t>RelatedPerson.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0}
 </t>
   </si>
   <si>
-    <t>Name of a human - parts and usage</t>
-  </si>
-  <si>
-    <t>A human's name with the ability to identify parts and usage.</t>
-  </si>
-  <si>
-    <t>Names may be changed, or repudiated, or people may have different names in different contexts. Names may be divided into parts of different type that have variable significance depending on context, though the division into parts does not always matter. With personal names, the different parts might or might not be imbued with some implicit meaning; various cultures associate different importance with the name parts and the degree to which systems must care about name parts around the world varies widely.</t>
+    <t>A name associated with the person</t>
+  </si>
+  <si>
+    <t>A name associated with the person.</t>
   </si>
   <si>
     <t>Related persons need to be identified by name, but it is uncommon to need details about multiple other names for that person.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
+    <t>name</t>
+  </si>
+  <si>
+    <t>NK1-2</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
-    <t>EN (actually, PN)</t>
-  </si>
-  <si>
-    <t>XPN</t>
-  </si>
-  <si>
-    <t>RelatedPerson.telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
-</t>
-  </si>
-  <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
-  </si>
-  <si>
-    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
+    <t>A contact detail for the person</t>
+  </si>
+  <si>
+    <t>A contact detail for the person, e.g. a telephone number or an email address.</t>
   </si>
   <si>
     <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
@@ -1054,14 +1050,10 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>TEL</t>
-  </si>
-  <si>
-    <t>XTN</t>
+    <t>telecom</t>
+  </si>
+  <si>
+    <t>NK1-5 / NK1-6 / NK1-40</t>
   </si>
   <si>
     <t>RelatedPerson.gender</t>
@@ -1110,26 +1102,23 @@
     <t>RelatedPerson.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
+    <t>Address where the related person can be contacted or visited</t>
+  </si>
+  <si>
+    <t>Address where the related person can be contacted or visited.</t>
   </si>
   <si>
     <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>
   </si>
   <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>XAD</t>
+    <t>addr</t>
+  </si>
+  <si>
+    <t>NK1-4</t>
   </si>
   <si>
     <t>RelatedPerson.photo</t>
@@ -1564,17 +1553,17 @@
   <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.2109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.68359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.5390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.81640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.94921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="70.10546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1583,25 +1572,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.609375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="36.79296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.59765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="31.73828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="85.921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="43.81640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="74.1171875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="37.796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2766,7 +2755,7 @@
         <v>77</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>77</v>
@@ -2831,10 +2820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2857,16 +2846,16 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2892,13 +2881,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2916,7 +2905,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2942,10 +2931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2968,16 +2957,16 @@
         <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3003,13 +2992,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3027,7 +3016,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3053,10 +3042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3082,13 +3071,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3138,7 +3127,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3164,10 +3153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3190,16 +3179,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3225,13 +3214,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3249,7 +3238,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3275,14 +3264,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3301,16 +3290,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3360,7 +3349,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3375,7 +3364,7 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
@@ -3386,14 +3375,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3412,16 +3401,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3471,7 +3460,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3486,7 +3475,7 @@
         <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
@@ -3497,10 +3486,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3529,7 +3518,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3582,7 +3571,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3597,7 +3586,7 @@
         <v>115</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>77</v>
@@ -3608,10 +3597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3637,16 +3626,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3695,7 +3684,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3710,7 +3699,7 @@
         <v>115</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
@@ -3721,10 +3710,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3747,17 +3736,17 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3806,7 +3795,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3821,21 +3810,21 @@
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3858,70 +3847,70 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="R21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="R21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3936,10 +3925,10 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3947,10 +3936,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3973,17 +3962,17 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4032,7 +4021,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>86</v>
@@ -4047,21 +4036,21 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4084,17 +4073,17 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4119,19 +4108,19 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4141,7 +4130,7 @@
         <v>113</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4156,24 +4145,24 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4195,17 +4184,17 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4230,11 +4219,11 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4252,7 +4241,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4267,21 +4256,21 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4387,10 +4376,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4498,10 +4487,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4524,19 +4513,19 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4585,7 +4574,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4600,21 +4589,21 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4720,10 +4709,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4831,10 +4820,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4860,16 +4849,16 @@
         <v>128</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4879,7 +4868,7 @@
         <v>77</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>77</v>
@@ -4918,7 +4907,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4933,21 +4922,21 @@
         <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4973,13 +4962,13 @@
         <v>100</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5029,7 +5018,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5044,21 +5033,21 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5081,17 +5070,17 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5140,7 +5129,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5155,21 +5144,21 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5195,14 +5184,14 @@
         <v>100</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5251,7 +5240,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5266,21 +5255,21 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5303,19 +5292,19 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5364,7 +5353,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5379,21 +5368,21 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5419,16 +5408,16 @@
         <v>100</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5477,7 +5466,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5492,24 +5481,24 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>77</v>
@@ -5531,17 +5520,17 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5566,11 +5555,11 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5588,7 +5577,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5603,21 +5592,21 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5723,10 +5712,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5834,10 +5823,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5860,19 +5849,19 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5921,7 +5910,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5936,21 +5925,21 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6056,10 +6045,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6167,10 +6156,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6196,16 +6185,16 @@
         <v>128</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6215,7 +6204,7 @@
         <v>77</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>77</v>
@@ -6254,7 +6243,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6269,21 +6258,21 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6309,13 +6298,13 @@
         <v>100</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6365,7 +6354,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6380,21 +6369,21 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6417,17 +6406,17 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6476,7 +6465,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6491,21 +6480,21 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6531,14 +6520,14 @@
         <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6587,7 +6576,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6602,21 +6591,21 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6639,19 +6628,19 @@
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6700,7 +6689,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6715,21 +6704,21 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6755,16 +6744,16 @@
         <v>100</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6813,7 +6802,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6828,21 +6817,21 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6862,20 +6851,18 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N48" t="s" s="2">
         <v>325</v>
       </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>326</v>
       </c>
@@ -6926,7 +6913,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6935,27 +6922,27 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6975,22 +6962,22 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7039,7 +7026,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7048,27 +7035,27 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>338</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7091,17 +7078,17 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7126,14 +7113,14 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y50" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7150,7 +7137,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7165,21 +7152,21 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7202,13 +7189,13 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7259,7 +7246,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7274,7 +7261,7 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>77</v>
@@ -7285,10 +7272,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7308,22 +7295,20 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7372,7 +7357,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7381,27 +7366,27 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7424,17 +7409,17 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7483,7 +7468,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7498,21 +7483,21 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7535,13 +7520,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7592,7 +7577,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7607,10 +7592,10 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7618,10 +7603,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7644,19 +7629,19 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7705,7 +7690,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7720,7 +7705,7 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -7731,10 +7716,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7840,10 +7825,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7951,14 +7936,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7980,16 +7965,16 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8038,7 +8023,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8053,7 +8038,7 @@
         <v>115</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>77</v>
@@ -8064,10 +8049,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8090,19 +8075,19 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8127,13 +8112,13 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8151,7 +8136,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>86</v>
@@ -8166,7 +8151,7 @@
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>77</v>
@@ -8177,10 +8162,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8203,19 +8188,19 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8264,7 +8249,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8279,7 +8264,7 @@
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>77</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-related-person.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-related-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="400">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -418,7 +418,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -431,14 +431,14 @@
     <t>RelatedPerson.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -460,9 +460,6 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0</t>
-  </si>
-  <si>
     <t>RelatedPerson.meta.security</t>
   </si>
   <si>
@@ -485,7 +482,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -509,7 +506,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -552,7 +549,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -691,7 +688,7 @@
     <t>RelatedPerson.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -726,7 +723,7 @@
     <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -751,7 +748,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:Role.id</t>
@@ -970,7 +967,7 @@
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:RelationType.id</t>
@@ -1012,36 +1009,43 @@
     <t>RelatedPerson.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
 </t>
   </si>
   <si>
-    <t>A name associated with the person</t>
-  </si>
-  <si>
-    <t>A name associated with the person.</t>
+    <t>Name of a human - parts and usage</t>
+  </si>
+  <si>
+    <t>A human's name with the ability to identify parts and usage.</t>
+  </si>
+  <si>
+    <t>Names may be changed, or repudiated, or people may have different names in different contexts. Names may be divided into parts of different type that have variable significance depending on context, though the division into parts does not always matter. With personal names, the different parts might or might not be imbued with some implicit meaning; various cultures associate different importance with the name parts and the degree to which systems must care about name parts around the world varies widely.</t>
   </si>
   <si>
     <t>Related persons need to be identified by name, but it is uncommon to need details about multiple other names for that person.</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>NK1-2</t>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>EN (actually, PN)</t>
+  </si>
+  <si>
+    <t>XPN</t>
   </si>
   <si>
     <t>RelatedPerson.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
-    <t>A contact detail for the person</t>
-  </si>
-  <si>
-    <t>A contact detail for the person, e.g. a telephone number or an email address.</t>
+    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
+  </si>
+  <si>
+    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
   </si>
   <si>
     <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
@@ -1050,10 +1054,14 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
-    <t>telecom</t>
-  </si>
-  <si>
-    <t>NK1-5 / NK1-6 / NK1-40</t>
+    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>TEL</t>
+  </si>
+  <si>
+    <t>XTN</t>
   </si>
   <si>
     <t>RelatedPerson.gender</t>
@@ -1102,23 +1110,26 @@
     <t>RelatedPerson.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
 </t>
   </si>
   <si>
-    <t>Address where the related person can be contacted or visited</t>
-  </si>
-  <si>
-    <t>Address where the related person can be contacted or visited.</t>
+    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
+  </si>
+  <si>
+    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
+  </si>
+  <si>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>
   </si>
   <si>
-    <t>addr</t>
-  </si>
-  <si>
-    <t>NK1-4</t>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>XAD</t>
   </si>
   <si>
     <t>RelatedPerson.photo</t>
@@ -1553,17 +1564,17 @@
   <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.2109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="44.68359375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.5390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="70.10546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="75.94921875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1572,25 +1583,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.59765625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="31.73828125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.609375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="74.1171875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="28.5078125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="37.796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="85.921875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="43.81640625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2755,7 +2766,7 @@
         <v>77</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>143</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>77</v>
@@ -2820,10 +2831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2846,16 +2857,16 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2881,31 +2892,31 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2931,10 +2942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2957,16 +2968,16 @@
         <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2992,31 +3003,31 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3042,10 +3053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3071,13 +3082,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3127,7 +3138,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3153,10 +3164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3179,16 +3190,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3214,31 +3225,31 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3264,14 +3275,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3290,16 +3301,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3349,7 +3360,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3364,7 +3375,7 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
@@ -3375,14 +3386,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3401,16 +3412,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3460,7 +3471,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3475,7 +3486,7 @@
         <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
@@ -3486,10 +3497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3518,7 +3529,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3571,7 +3582,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3586,7 +3597,7 @@
         <v>115</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>77</v>
@@ -3597,10 +3608,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3626,16 +3637,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3684,7 +3695,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3699,7 +3710,7 @@
         <v>115</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
@@ -3710,10 +3721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3736,17 +3747,17 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3795,7 +3806,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3810,21 +3821,21 @@
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>206</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3847,26 +3858,26 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="O21" t="s" s="2">
+      <c r="P21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="P21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q21" t="s" s="2">
-        <v>213</v>
-      </c>
       <c r="R21" t="s" s="2">
         <v>77</v>
       </c>
@@ -3910,7 +3921,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3925,10 +3936,10 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3936,10 +3947,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3962,17 +3973,17 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4021,7 +4032,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>86</v>
@@ -4036,21 +4047,21 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4073,17 +4084,17 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4108,19 +4119,19 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Z23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4130,7 +4141,7 @@
         <v>113</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4145,24 +4156,24 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4184,17 +4195,17 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4219,11 +4230,11 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4241,7 +4252,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4256,21 +4267,21 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4376,10 +4387,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4487,10 +4498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4513,19 +4524,19 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4574,7 +4585,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4589,21 +4600,21 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>249</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4709,10 +4720,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4820,10 +4831,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4849,16 +4860,16 @@
         <v>128</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4868,46 +4879,46 @@
         <v>77</v>
       </c>
       <c r="S30" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4922,21 +4933,21 @@
         <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4962,13 +4973,13 @@
         <v>100</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5018,7 +5029,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5033,21 +5044,21 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5070,17 +5081,17 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5129,7 +5140,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5144,21 +5155,21 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>279</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5184,14 +5195,14 @@
         <v>100</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5240,7 +5251,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5255,21 +5266,21 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5292,19 +5303,19 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5353,7 +5364,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5368,21 +5379,21 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5408,16 +5419,16 @@
         <v>100</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5466,7 +5477,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5481,24 +5492,24 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>77</v>
@@ -5520,17 +5531,17 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5555,11 +5566,11 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5577,7 +5588,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5592,21 +5603,21 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5712,10 +5723,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5823,10 +5834,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5849,19 +5860,19 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5910,7 +5921,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5925,21 +5936,21 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>249</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6045,10 +6056,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6156,10 +6167,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6185,16 +6196,16 @@
         <v>128</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6204,7 +6215,7 @@
         <v>77</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>77</v>
@@ -6243,7 +6254,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6258,21 +6269,21 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6298,13 +6309,13 @@
         <v>100</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6354,7 +6365,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6369,21 +6380,21 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6406,17 +6417,17 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6465,7 +6476,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6480,21 +6491,21 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>279</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6520,14 +6531,14 @@
         <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6576,7 +6587,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6591,21 +6602,21 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6628,19 +6639,19 @@
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6689,7 +6700,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6704,21 +6715,21 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6744,16 +6755,16 @@
         <v>100</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6802,7 +6813,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6817,21 +6828,21 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6851,18 +6862,20 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>326</v>
       </c>
@@ -6913,7 +6926,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6922,27 +6935,27 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>327</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6962,22 +6975,22 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7026,7 +7039,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7035,27 +7048,27 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>327</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>336</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7078,17 +7091,17 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7113,13 +7126,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7137,7 +7150,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7152,21 +7165,21 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7189,13 +7202,13 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7246,7 +7259,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7261,7 +7274,7 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>77</v>
@@ -7272,10 +7285,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7295,20 +7308,22 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7357,7 +7372,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7366,27 +7381,27 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>327</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7409,17 +7424,17 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7468,7 +7483,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7483,21 +7498,21 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7520,13 +7535,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7577,7 +7592,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7592,10 +7607,10 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7603,10 +7618,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7629,19 +7644,19 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7690,7 +7705,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7705,7 +7720,7 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -7716,10 +7731,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7825,10 +7840,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7936,14 +7951,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7965,16 +7980,16 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8023,7 +8038,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8038,7 +8053,7 @@
         <v>115</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>77</v>
@@ -8049,10 +8064,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8075,19 +8090,19 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8112,14 +8127,14 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y59" t="s" s="2">
+      <c r="Z59" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8136,7 +8151,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>86</v>
@@ -8151,7 +8166,7 @@
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>77</v>
@@ -8162,10 +8177,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8188,19 +8203,19 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8249,7 +8264,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8264,7 +8279,7 @@
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>77</v>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-related-person.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-related-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="397">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson</t>
+    <t>http://hl7.org/fhir/StructureDefinition/RelatedPerson|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -418,7 +418,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -431,14 +431,14 @@
     <t>RelatedPerson.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -460,6 +460,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.2.0</t>
+  </si>
+  <si>
     <t>RelatedPerson.meta.security</t>
   </si>
   <si>
@@ -482,7 +485,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -506,7 +509,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -549,7 +552,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -688,7 +691,7 @@
     <t>RelatedPerson.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -723,7 +726,7 @@
     <t>We need to know the relationship with the patient since it influences the interpretation of the information attributed to this person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype</t>
+    <t>http://hl7.org/fhir/ValueSet/relatedperson-relationshiptype|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -748,7 +751,7 @@
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role|2.2.0</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:Role.id</t>
@@ -967,7 +970,7 @@
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type|2.2.0</t>
   </si>
   <si>
     <t>RelatedPerson.relationship:RelationType.id</t>
@@ -1009,43 +1012,36 @@
     <t>RelatedPerson.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0}
 </t>
   </si>
   <si>
-    <t>Name of a human - parts and usage</t>
-  </si>
-  <si>
-    <t>A human's name with the ability to identify parts and usage.</t>
-  </si>
-  <si>
-    <t>Names may be changed, or repudiated, or people may have different names in different contexts. Names may be divided into parts of different type that have variable significance depending on context, though the division into parts does not always matter. With personal names, the different parts might or might not be imbued with some implicit meaning; various cultures associate different importance with the name parts and the degree to which systems must care about name parts around the world varies widely.</t>
+    <t>A name associated with the person</t>
+  </si>
+  <si>
+    <t>A name associated with the person.</t>
   </si>
   <si>
     <t>Related persons need to be identified by name, but it is uncommon to need details about multiple other names for that person.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
+    <t>name</t>
+  </si>
+  <si>
+    <t>NK1-2</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
-    <t>EN (actually, PN)</t>
-  </si>
-  <si>
-    <t>XPN</t>
-  </si>
-  <si>
-    <t>RelatedPerson.telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
-</t>
-  </si>
-  <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
-  </si>
-  <si>
-    <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
+    <t>A contact detail for the person</t>
+  </si>
+  <si>
+    <t>A contact detail for the person, e.g. a telephone number or an email address.</t>
   </si>
   <si>
     <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently, and also to help with identification.</t>
@@ -1054,14 +1050,10 @@
     <t>People have (primary) ways to contact them in some way such as phone, email.</t>
   </si>
   <si>
-    <t>cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}
-ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
-  </si>
-  <si>
-    <t>TEL</t>
-  </si>
-  <si>
-    <t>XTN</t>
+    <t>telecom</t>
+  </si>
+  <si>
+    <t>NK1-5 / NK1-6 / NK1-40</t>
   </si>
   <si>
     <t>RelatedPerson.gender</t>
@@ -1110,26 +1102,23 @@
     <t>RelatedPerson.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
-  </si>
-  <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
-  </si>
-  <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
+    <t>Address where the related person can be contacted or visited</t>
+  </si>
+  <si>
+    <t>Address where the related person can be contacted or visited.</t>
   </si>
   <si>
     <t>Need to keep track where the related person can be contacted per postal mail or visited.</t>
   </si>
   <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>XAD</t>
+    <t>addr</t>
+  </si>
+  <si>
+    <t>NK1-4</t>
   </si>
   <si>
     <t>RelatedPerson.photo</t>
@@ -1564,17 +1553,17 @@
   <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.2109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.68359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.5390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.81640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.94921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="70.10546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1583,25 +1572,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.609375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="36.79296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.59765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="31.73828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="85.921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="43.81640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="74.1171875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="37.796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2766,7 +2755,7 @@
         <v>77</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>77</v>
@@ -2831,10 +2820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2857,16 +2846,16 @@
         <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2892,13 +2881,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2916,7 +2905,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2942,10 +2931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2968,16 +2957,16 @@
         <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3003,13 +2992,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3027,7 +3016,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3053,10 +3042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3082,13 +3071,13 @@
         <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3138,7 +3127,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3164,10 +3153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3190,16 +3179,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3225,13 +3214,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3249,7 +3238,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3275,14 +3264,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3301,16 +3290,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3360,7 +3349,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3375,7 +3364,7 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
@@ -3386,14 +3375,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3412,16 +3401,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3471,7 +3460,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3486,7 +3475,7 @@
         <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
@@ -3497,10 +3486,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3529,7 +3518,7 @@
         <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>110</v>
@@ -3582,7 +3571,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3597,7 +3586,7 @@
         <v>115</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>77</v>
@@ -3608,10 +3597,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3637,16 +3626,16 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3695,7 +3684,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3710,7 +3699,7 @@
         <v>115</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
@@ -3721,10 +3710,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3747,17 +3736,17 @@
         <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3806,7 +3795,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3821,21 +3810,21 @@
         <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3858,70 +3847,70 @@
         <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="R21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="R21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3936,10 +3925,10 @@
         <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3947,10 +3936,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3973,17 +3962,17 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4032,7 +4021,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>86</v>
@@ -4047,21 +4036,21 @@
         <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4084,17 +4073,17 @@
         <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4119,19 +4108,19 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -4141,7 +4130,7 @@
         <v>113</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4156,24 +4145,24 @@
         <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4195,17 +4184,17 @@
         <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4230,11 +4219,11 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4252,7 +4241,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4267,21 +4256,21 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4387,10 +4376,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4498,10 +4487,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4524,19 +4513,19 @@
         <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4585,7 +4574,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4600,21 +4589,21 @@
         <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4720,10 +4709,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4831,10 +4820,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4860,16 +4849,16 @@
         <v>128</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4879,7 +4868,7 @@
         <v>77</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>77</v>
@@ -4918,7 +4907,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4933,21 +4922,21 @@
         <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4973,13 +4962,13 @@
         <v>100</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5029,7 +5018,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5044,21 +5033,21 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5081,17 +5070,17 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5140,7 +5129,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5155,21 +5144,21 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5195,14 +5184,14 @@
         <v>100</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5251,7 +5240,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5266,21 +5255,21 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5303,19 +5292,19 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5364,7 +5353,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5379,21 +5368,21 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5419,16 +5408,16 @@
         <v>100</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5477,7 +5466,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5492,24 +5481,24 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>77</v>
@@ -5531,17 +5520,17 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5566,11 +5555,11 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5588,7 +5577,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5603,21 +5592,21 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5723,10 +5712,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5834,10 +5823,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5860,19 +5849,19 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5921,7 +5910,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5936,21 +5925,21 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6056,10 +6045,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6167,10 +6156,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6196,16 +6185,16 @@
         <v>128</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -6215,7 +6204,7 @@
         <v>77</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>77</v>
@@ -6254,7 +6243,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6269,21 +6258,21 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6309,13 +6298,13 @@
         <v>100</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6365,7 +6354,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6380,21 +6369,21 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6417,17 +6406,17 @@
         <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6476,7 +6465,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6491,21 +6480,21 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6531,14 +6520,14 @@
         <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6587,7 +6576,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6602,21 +6591,21 @@
         <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6639,19 +6628,19 @@
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6700,7 +6689,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6715,21 +6704,21 @@
         <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6755,16 +6744,16 @@
         <v>100</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6813,7 +6802,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6828,21 +6817,21 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6862,20 +6851,18 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N48" t="s" s="2">
         <v>325</v>
       </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
         <v>326</v>
       </c>
@@ -6926,7 +6913,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6935,27 +6922,27 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6975,22 +6962,22 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7039,7 +7026,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7048,27 +7035,27 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>338</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7091,17 +7078,17 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7126,14 +7113,14 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y50" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7150,7 +7137,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7165,21 +7152,21 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7202,13 +7189,13 @@
         <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7259,7 +7246,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7274,7 +7261,7 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>77</v>
@@ -7285,10 +7272,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7308,22 +7295,20 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7372,7 +7357,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7381,27 +7366,27 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7424,17 +7409,17 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7483,7 +7468,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7498,21 +7483,21 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7535,13 +7520,13 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7592,7 +7577,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7607,10 +7592,10 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7618,10 +7603,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7644,19 +7629,19 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7705,7 +7690,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7720,7 +7705,7 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -7731,10 +7716,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7840,10 +7825,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7951,14 +7936,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7980,16 +7965,16 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>110</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8038,7 +8023,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8053,7 +8038,7 @@
         <v>115</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>77</v>
@@ -8064,10 +8049,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8090,19 +8075,19 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8127,13 +8112,13 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8151,7 +8136,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>86</v>
@@ -8166,7 +8151,7 @@
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>77</v>
@@ -8177,10 +8162,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8203,19 +8188,19 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8264,7 +8249,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8279,7 +8264,7 @@
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>77</v>
